--- a/docs/Data architecture/Entities/StudyBlock.xlsx
+++ b/docs/Data architecture/Entities/StudyBlock.xlsx
@@ -8,15 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Computer Science\Programming\C#\Projects\RealProjects\NeUrokAdmin\docs\Data architecture\Entities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9001DE2A-40FE-4E3A-B5D4-29A32F7E3233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66628203-061A-4927-8EF9-73163D3F5DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2385" yWindow="1290" windowWidth="23805" windowHeight="14220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="1290" windowWidth="23805" windowHeight="13440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="subscriptions" sheetId="1" r:id="rId1"/>
     <sheet name="students" sheetId="3" r:id="rId2"/>
-    <sheet name="subscriptlon_statuses" sheetId="4" r:id="rId3"/>
-    <sheet name="class_types" sheetId="2" r:id="rId4"/>
+    <sheet name="student_subscriptions" sheetId="5" r:id="rId3"/>
+    <sheet name="attendances" sheetId="6" r:id="rId4"/>
+    <sheet name="groups" sheetId="9" r:id="rId5"/>
+    <sheet name="group_students" sheetId="11" r:id="rId6"/>
+    <sheet name="group_dates" sheetId="10" r:id="rId7"/>
+    <sheet name="attendance_statuses" sheetId="8" r:id="rId8"/>
+    <sheet name="attendance_types" sheetId="12" r:id="rId9"/>
+    <sheet name="teachers" sheetId="7" r:id="rId10"/>
+    <sheet name="subscriptlon_statuses" sheetId="4" r:id="rId11"/>
+    <sheet name="class_types" sheetId="2" r:id="rId12"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -94,6 +102,66 @@
   </si>
   <si>
     <t>subscription_finish_date</t>
+  </si>
+  <si>
+    <t>student_id</t>
+  </si>
+  <si>
+    <t>course_id</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>fullname</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Малькина Оксана Владимировна</t>
+  </si>
+  <si>
+    <t>teacher_id</t>
+  </si>
+  <si>
+    <t>is_completed</t>
+  </si>
+  <si>
+    <t>attendance_status_id</t>
+  </si>
+  <si>
+    <t>Присутствовал</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>week_days</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>Уважительная причина</t>
+  </si>
+  <si>
+    <t>Прогул</t>
+  </si>
+  <si>
+    <t>Стандарт</t>
+  </si>
+  <si>
+    <t>Отработка</t>
+  </si>
+  <si>
+    <t>attendance_type_id</t>
+  </si>
+  <si>
+    <t>class_type_id</t>
   </si>
 </sst>
 </file>
@@ -150,12 +218,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -536,83 +605,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5DD45F-58A1-4A16-A800-7AE58471A580}">
-  <dimension ref="A1:G3"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0591B481-26D2-4C86-A301-6C5E3390AD6B}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>46090</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45013</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>11</v>
-      </c>
-      <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2">
-        <v>46132</v>
-      </c>
-      <c r="G3" s="2">
-        <v>46133</v>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8224B9A-58B7-47F5-AFA0-E2C020D242D0}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -666,7 +684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC47DBD-165C-4581-842C-2CEC1C30E02A}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -710,4 +728,409 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5DD45F-58A1-4A16-A800-7AE58471A580}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0488B1F7-9CA6-48E2-A7EF-89CBF6E399A4}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46090</v>
+      </c>
+      <c r="H2" s="2">
+        <v>45013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46132</v>
+      </c>
+      <c r="H3" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A44D75-E3D8-4AC4-9038-B0F120900A43}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46093.708333333336</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>46094.708333333336</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14E0EE8-E4A5-43B1-80BF-93DB949DF933}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C59C2A8-BA25-4444-A828-CD5212D3F2CD}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27F3534-7478-4BD8-A0CA-1D70310293F1}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8D229B-8508-43B0-9E95-CC582AB3EA98}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52C65AC-912A-4623-A8AA-A3FB7466EFF4}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/Data architecture/Entities/StudyBlock.xlsx
+++ b/docs/Data architecture/Entities/StudyBlock.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Computer Science\Programming\C#\Projects\RealProjects\NeUrokAdmin\docs\Data architecture\Entities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66628203-061A-4927-8EF9-73163D3F5DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31C2208A-306A-41B2-A679-70432AB04CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="1290" windowWidth="23805" windowHeight="13440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4365" yWindow="1290" windowWidth="23805" windowHeight="13440" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="subscriptions" sheetId="1" r:id="rId1"/>
     <sheet name="students" sheetId="3" r:id="rId2"/>
     <sheet name="student_subscriptions" sheetId="5" r:id="rId3"/>
-    <sheet name="attendances" sheetId="6" r:id="rId4"/>
-    <sheet name="groups" sheetId="9" r:id="rId5"/>
-    <sheet name="group_students" sheetId="11" r:id="rId6"/>
-    <sheet name="group_dates" sheetId="10" r:id="rId7"/>
+    <sheet name="groups" sheetId="9" r:id="rId4"/>
+    <sheet name="group_students" sheetId="11" r:id="rId5"/>
+    <sheet name="group_dates" sheetId="10" r:id="rId6"/>
+    <sheet name="attendances" sheetId="6" r:id="rId7"/>
     <sheet name="attendance_statuses" sheetId="8" r:id="rId8"/>
     <sheet name="attendance_types" sheetId="12" r:id="rId9"/>
     <sheet name="teachers" sheetId="7" r:id="rId10"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -866,6 +866,82 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14E0EE8-E4A5-43B1-80BF-93DB949DF933}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C59C2A8-BA25-4444-A828-CD5212D3F2CD}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27F3534-7478-4BD8-A0CA-1D70310293F1}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7A44D75-E3D8-4AC4-9038-B0F120900A43}">
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -979,79 +1055,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14E0EE8-E4A5-43B1-80BF-93DB949DF933}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C59C2A8-BA25-4444-A828-CD5212D3F2CD}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27F3534-7478-4BD8-A0CA-1D70310293F1}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8D229B-8508-43B0-9E95-CC582AB3EA98}">
   <dimension ref="A1:B4"/>

--- a/docs/Data architecture/Entities/StudyBlock.xlsx
+++ b/docs/Data architecture/Entities/StudyBlock.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Computer Science\Programming\C#\Projects\RealProjects\NeUrokAdmin\docs\Data architecture\Entities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66628203-061A-4927-8EF9-73163D3F5DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88312BFC-F239-4583-BC80-7E930423B7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4365" yWindow="1290" windowWidth="23805" windowHeight="13440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="1005" windowWidth="23805" windowHeight="13440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="subscriptions" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,14 @@
     <sheet name="student_subscriptions" sheetId="5" r:id="rId3"/>
     <sheet name="attendances" sheetId="6" r:id="rId4"/>
     <sheet name="groups" sheetId="9" r:id="rId5"/>
-    <sheet name="group_students" sheetId="11" r:id="rId6"/>
-    <sheet name="group_dates" sheetId="10" r:id="rId7"/>
-    <sheet name="attendance_statuses" sheetId="8" r:id="rId8"/>
-    <sheet name="attendance_types" sheetId="12" r:id="rId9"/>
-    <sheet name="teachers" sheetId="7" r:id="rId10"/>
-    <sheet name="subscriptlon_statuses" sheetId="4" r:id="rId11"/>
-    <sheet name="class_types" sheetId="2" r:id="rId12"/>
+    <sheet name="group_statuses" sheetId="13" r:id="rId6"/>
+    <sheet name="group_students" sheetId="11" r:id="rId7"/>
+    <sheet name="group_dates" sheetId="10" r:id="rId8"/>
+    <sheet name="attendance_statuses" sheetId="8" r:id="rId9"/>
+    <sheet name="attendance_types" sheetId="12" r:id="rId10"/>
+    <sheet name="teachers" sheetId="7" r:id="rId11"/>
+    <sheet name="subscriptlon_statuses" sheetId="4" r:id="rId12"/>
+    <sheet name="class_types" sheetId="2" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="47">
   <si>
     <t>id</t>
   </si>
@@ -162,6 +163,21 @@
   </si>
   <si>
     <t>class_type_id</t>
+  </si>
+  <si>
+    <t>В наборе</t>
+  </si>
+  <si>
+    <t>Набрана</t>
+  </si>
+  <si>
+    <t>Активна</t>
+  </si>
+  <si>
+    <t>Закрыта</t>
+  </si>
+  <si>
+    <t>group_status_id</t>
   </si>
 </sst>
 </file>
@@ -606,6 +622,43 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52C65AC-912A-4623-A8AA-A3FB7466EFF4}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0591B481-26D2-4C86-A301-6C5E3390AD6B}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -638,7 +691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8224B9A-58B7-47F5-AFA0-E2C020D242D0}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -684,7 +737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC47DBD-165C-4581-842C-2CEC1C30E02A}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -981,14 +1034,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E14E0EE8-E4A5-43B1-80BF-93DB949DF933}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1002,9 +1057,12 @@
         <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1014,6 +1072,56 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2A2C6F-A12C-4B7C-AD29-59120317EF35}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C59C2A8-BA25-4444-A828-CD5212D3F2CD}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1034,7 +1142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27F3534-7478-4BD8-A0CA-1D70310293F1}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1052,7 +1160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8D229B-8508-43B0-9E95-CC582AB3EA98}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1096,41 +1204,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52C65AC-912A-4623-A8AA-A3FB7466EFF4}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>